--- a/Draft_Memo_Template.xlsx
+++ b/Draft_Memo_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\vcr automasi - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C4A663B-94AF-40CB-AAE2-8FF197CADA9D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E085B94-3B71-4655-8ABC-534A23ADB023}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ADD867E7-D695-47CD-BB5D-473DC93B08FD}"/>
   </bookViews>
@@ -396,350 +396,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
+  <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>134471</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>41461</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>739588</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>11205</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="TextBox 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9BDFCD4-4B0A-5BF2-D978-D5A4B21C670E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="134471" y="7414932"/>
-          <a:ext cx="1568823" cy="597273"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="sng"/>
-            <a:t>Dina Murdaningrum</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none"/>
-            <a:t>Asst Mgr</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none" baseline="0"/>
-            <a:t> Cust Dev</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none"/>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>862853</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>41461</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2431676</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>11205</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="TextBox 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EB316108-246F-C80A-9FF4-DD3E84BDA869}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1826559" y="7414932"/>
-          <a:ext cx="1568823" cy="597273"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="sng"/>
-            <a:t>Elly Erosa</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none"/>
-            <a:t>Mgr</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none" baseline="0"/>
-            <a:t> Cust Dev</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none"/>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2274795</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>41461</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>593912</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>11205</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{69772701-67C6-00EB-3DB4-90851EAAF0D0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3238501" y="7414932"/>
-          <a:ext cx="1568823" cy="597273"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="sng"/>
-            <a:t>Didin Nazmudin</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none"/>
-            <a:t>GM </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none" baseline="0"/>
-            <a:t>Cust Dev</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none"/>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>806825</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>41461</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>9525</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>336178</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>11205</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F424A76-E570-F0BA-7DD8-F4139BA6378B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5020237" y="7414932"/>
-          <a:ext cx="1568823" cy="597273"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="sng"/>
-            <a:t>Rizky Aprilianto</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none"/>
-            <a:t>Head</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="1100" u="none" baseline="0"/>
-            <a:t> of Store Support</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-US" sz="1100" u="none"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>1041769</xdr:colOff>
-      <xdr:row>32</xdr:row>
-      <xdr:rowOff>81060</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2228851</xdr:colOff>
+      <xdr:colOff>343780</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>38101</xdr:rowOff>
+      <xdr:rowOff>409776</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
+        <xdr:cNvPr id="9" name="Picture 8">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FAA05C31-7A5F-4C82-8687-78622D726982}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A7C89CD-6CE2-4350-89A6-5249AE717B28}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -755,55 +430,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2003794" y="6434235"/>
-          <a:ext cx="1187082" cy="976216"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="absolute">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>9526</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>209749</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="Picture 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BE5A6EE3-C1AD-48BF-8F2D-341C14DE0C70}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="295276" y="6734175"/>
-          <a:ext cx="1314449" cy="590749"/>
+          <a:off x="295275" y="6343650"/>
+          <a:ext cx="6306430" cy="1438476"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1470,7 +1098,7 @@
     <mergeCell ref="A26:H26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.1" header="0.3" footer="0.7"/>
-  <pageSetup scale="81" orientation="portrait" r:id="rId1"/>
+  <pageSetup scale="84" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Draft_Memo_Template.xlsx
+++ b/Draft_Memo_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\vcr automasi - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E085B94-3B71-4655-8ABC-534A23ADB023}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DA489E-7F4D-4AAA-BADD-9B99CBB3CFDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ADD867E7-D695-47CD-BB5D-473DC93B08FD}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="MEMOTRANSAKSI" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">MEMOTRANSAKSI!$A$1:$H$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">MEMOTRANSAKSI!$A$1:$I$42</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
   <si>
     <t>MEMO PERSETUJUAN PELAKSANAAN TRANSAKSI</t>
   </si>
@@ -136,12 +136,18 @@
   </si>
   <si>
     <t>Total transfer</t>
+  </si>
+  <si>
+    <t>Rp.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="_([$Rp-421]* #,##0_);_([$Rp-421]* \(#,##0\);_([$Rp-421]* &quot;-&quot;_);_(@_)"/>
+  </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -306,9 +312,6 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -323,6 +326,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -352,7 +358,7 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
+      <xdr:col>9</xdr:col>
       <xdr:colOff>19050</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
@@ -404,8 +410,8 @@
       <xdr:rowOff>180975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>343780</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>305680</xdr:colOff>
       <xdr:row>37</xdr:row>
       <xdr:rowOff>409776</xdr:rowOff>
     </xdr:to>
@@ -767,19 +773,20 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A6:N38"/>
+  <dimension ref="A6:O38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="3" max="3" width="1" customWidth="1"/>
     <col min="4" max="4" width="45.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="3.5703125" customWidth="1"/>
-    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.42578125" customWidth="1"/>
-    <col min="9" max="9" width="3.28515625" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" customWidth="1"/>
+    <col min="10" max="10" width="3.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -788,11 +795,11 @@
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
         <v>28</v>
       </c>
@@ -805,8 +812,9 @@
       </c>
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
-    </row>
-    <row r="8" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G7" s="20"/>
+    </row>
+    <row r="8" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
         <v>26</v>
       </c>
@@ -819,8 +827,9 @@
       <c r="F8" s="19"/>
       <c r="G8" s="19"/>
       <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I8" s="19"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="4"/>
       <c r="C9" s="19"/>
       <c r="D9" s="19"/>
@@ -828,38 +837,41 @@
       <c r="F9" s="19"/>
       <c r="G9" s="19"/>
       <c r="H9" s="19"/>
-    </row>
-    <row r="10" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="28" t="s">
+      <c r="I9" s="19"/>
+    </row>
+    <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="28"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="28"/>
-      <c r="H10" s="28"/>
-      <c r="I10" s="5"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="27"/>
+      <c r="C10" s="27"/>
+      <c r="D10" s="27"/>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="27"/>
+      <c r="H10" s="27"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="5"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="29" t="s">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="29"/>
+      <c r="B12" s="28"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
       <c r="F12" s="6"/>
       <c r="G12" s="6"/>
-      <c r="H12" s="7"/>
+      <c r="H12" s="6"/>
       <c r="I12" s="7"/>
       <c r="J12" s="7"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K12" s="7"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>2</v>
       </c>
@@ -874,27 +886,29 @@
       <c r="G13" s="8"/>
       <c r="H13" s="8"/>
       <c r="I13" s="8"/>
-      <c r="J13" s="7"/>
-    </row>
-    <row r="14" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="J13" s="8"/>
+      <c r="K13" s="7"/>
+    </row>
+    <row r="14" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" s="9"/>
       <c r="B14" s="10"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="30" t="s">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="30"/>
-      <c r="G15" s="30"/>
-      <c r="H15" s="30"/>
-      <c r="I15" s="4"/>
+      <c r="B15" s="29"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
       <c r="J15" s="4"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>4</v>
       </c>
@@ -908,8 +922,9 @@
       <c r="F16" s="22" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G16" s="22"/>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>6</v>
       </c>
@@ -923,8 +938,9 @@
       <c r="F17" s="21" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G17" s="21"/>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>7</v>
       </c>
@@ -936,8 +952,9 @@
         <v>5</v>
       </c>
       <c r="F18" s="25"/>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G18" s="25"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
         <v>9</v>
       </c>
@@ -948,9 +965,12 @@
       <c r="E19" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="26"/>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F19" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G19" s="8"/>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
         <v>10</v>
       </c>
@@ -961,9 +981,12 @@
       <c r="E20" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="26"/>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F20" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G20" s="8"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
         <v>11</v>
       </c>
@@ -975,9 +998,12 @@
       <c r="E21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="26"/>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F21" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="G21" s="8"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
         <v>13</v>
       </c>
@@ -989,12 +1015,13 @@
       <c r="E22" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="27"/>
-      <c r="G22" s="14"/>
+      <c r="F22" s="26"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="14"/>
       <c r="I22" s="14"/>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J22" s="14"/>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
         <v>15</v>
       </c>
@@ -1007,8 +1034,9 @@
         <v>5</v>
       </c>
       <c r="F23" s="8"/>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G23" s="8"/>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>16</v>
       </c>
@@ -1023,64 +1051,66 @@
       <c r="F24" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="G24" s="8"/>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="9"/>
     </row>
-    <row r="26" spans="1:14" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+    <row r="26" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="30" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="31"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="31"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="31"/>
-      <c r="H26" s="31"/>
-      <c r="N26" t="s">
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="O26" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="17"/>
     </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
     </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
     </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="9"/>
     </row>
-    <row r="37" spans="1:8" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:9" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="4"/>
       <c r="D37" s="24"/>
     </row>
-    <row r="38" spans="1:8" s="18" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:9" s="18" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="23"/>
       <c r="B38" s="23"/>
       <c r="C38" s="23"/>
@@ -1089,13 +1119,14 @@
       <c r="F38" s="23"/>
       <c r="G38" s="23"/>
       <c r="H38" s="23"/>
+      <c r="I38" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A10:H10"/>
+    <mergeCell ref="A10:I10"/>
     <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A26:H26"/>
+    <mergeCell ref="A15:I15"/>
+    <mergeCell ref="A26:I26"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.1" header="0.3" footer="0.7"/>
   <pageSetup scale="84" orientation="portrait" r:id="rId1"/>

--- a/Draft_Memo_Template.xlsx
+++ b/Draft_Memo_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\vcr automasi - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0DA489E-7F4D-4AAA-BADD-9B99CBB3CFDC}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468076F5-0C7B-47D0-BD7F-1F784B278DC3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ADD867E7-D695-47CD-BB5D-473DC93B08FD}"/>
   </bookViews>
@@ -315,6 +315,9 @@
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -326,9 +329,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -840,27 +840,27 @@
       <c r="I9" s="19"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="27"/>
-      <c r="C10" s="27"/>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="27"/>
-      <c r="G10" s="27"/>
-      <c r="H10" s="27"/>
-      <c r="I10" s="27"/>
+      <c r="B10" s="28"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="28"/>
+      <c r="F10" s="28"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="28"/>
       <c r="J10" s="5"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="28" t="s">
+      <c r="A12" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="B12" s="28"/>
+      <c r="B12" s="29"/>
       <c r="C12" s="6"/>
       <c r="D12" s="6"/>
       <c r="E12" s="6"/>
@@ -894,17 +894,17 @@
       <c r="B14" s="10"/>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="29" t="s">
+      <c r="A15" s="30" t="s">
         <v>3</v>
       </c>
-      <c r="B15" s="29"/>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="30"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="30"/>
+      <c r="I15" s="30"/>
       <c r="J15" s="4"/>
       <c r="K15" s="4"/>
     </row>
@@ -965,7 +965,7 @@
       <c r="E19" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F19" s="31" t="s">
+      <c r="F19" s="27" t="s">
         <v>35</v>
       </c>
       <c r="G19" s="8"/>
@@ -981,7 +981,7 @@
       <c r="E20" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="31" t="s">
+      <c r="F20" s="27" t="s">
         <v>35</v>
       </c>
       <c r="G20" s="8"/>
@@ -998,7 +998,7 @@
       <c r="E21" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="F21" s="31" t="s">
+      <c r="F21" s="27" t="s">
         <v>35</v>
       </c>
       <c r="G21" s="8"/>
@@ -1057,17 +1057,17 @@
       <c r="A25" s="9"/>
     </row>
     <row r="26" spans="1:15" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="30" t="s">
+      <c r="A26" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
       <c r="O26" t="s">
         <v>22</v>
       </c>

--- a/Draft_Memo_Template.xlsx
+++ b/Draft_Memo_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\vcr automasi - Copy\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{468076F5-0C7B-47D0-BD7F-1F784B278DC3}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62DB4F93-6237-4D8B-82D9-43B4FC300654}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{ADD867E7-D695-47CD-BB5D-473DC93B08FD}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
   <si>
     <t>MEMO PERSETUJUAN PELAKSANAAN TRANSAKSI</t>
   </si>
@@ -118,9 +118,6 @@
   </si>
   <si>
     <t xml:space="preserve">Perihal        </t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Jakarta, 1 Juli 2026</t>
   </si>
   <si>
     <t>No. Kartu Lotte Member PT BRIKONSUL BISNIS INDONESIA</t>
@@ -795,9 +792,7 @@
         <v>5</v>
       </c>
       <c r="D6" s="3"/>
-      <c r="I6" s="2" t="s">
-        <v>29</v>
-      </c>
+      <c r="I6" s="2"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -913,14 +908,14 @@
         <v>4</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C16" s="8"/>
       <c r="E16" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F16" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G16" s="22"/>
     </row>
@@ -929,14 +924,14 @@
         <v>6</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C17" s="12"/>
       <c r="E17" s="8" t="s">
         <v>5</v>
       </c>
       <c r="F17" s="21" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G17" s="21"/>
     </row>
@@ -966,7 +961,7 @@
         <v>5</v>
       </c>
       <c r="F19" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G19" s="8"/>
     </row>
@@ -982,7 +977,7 @@
         <v>5</v>
       </c>
       <c r="F20" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G20" s="8"/>
     </row>
@@ -991,7 +986,7 @@
         <v>11</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -999,7 +994,7 @@
         <v>5</v>
       </c>
       <c r="F21" s="27" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G21" s="8"/>
     </row>
